--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  28.07.2025 a 03.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  28.07.2025 a 03.08.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACA18BF-13BD-4793-9576-50A306BBD245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8DC94D-4A6D-4E15-B955-EB1933215654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,88 +54,67 @@
     <t>Relatório de Recusas  28.07.2025 a 03.08.2025</t>
   </si>
   <si>
-    <t>133504097</t>
+    <t>133496787</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório Recusas Santander- 30.07.2025</t>
-  </si>
-  <si>
-    <t>133526689</t>
-  </si>
-  <si>
-    <t>133555256</t>
-  </si>
-  <si>
-    <t>133566143</t>
-  </si>
-  <si>
-    <t>133579366</t>
-  </si>
-  <si>
-    <t>133573449</t>
-  </si>
-  <si>
-    <t>133577084</t>
-  </si>
-  <si>
-    <t>133598586</t>
-  </si>
-  <si>
-    <t>133674150</t>
-  </si>
-  <si>
-    <t>133443445</t>
-  </si>
-  <si>
-    <t>133478595</t>
-  </si>
-  <si>
-    <t>133624168</t>
-  </si>
-  <si>
-    <t>133530544</t>
-  </si>
-  <si>
-    <t>133547863</t>
-  </si>
-  <si>
-    <t>133550294</t>
-  </si>
-  <si>
-    <t>133554643</t>
-  </si>
-  <si>
-    <t>133555247</t>
-  </si>
-  <si>
-    <t>133556955</t>
-  </si>
-  <si>
-    <t>133558863</t>
-  </si>
-  <si>
-    <t>133562145</t>
-  </si>
-  <si>
-    <t>133565161</t>
-  </si>
-  <si>
-    <t>133565512</t>
-  </si>
-  <si>
-    <t>133623645</t>
-  </si>
-  <si>
-    <t>133570091</t>
-  </si>
-  <si>
-    <t>133578173</t>
-  </si>
-  <si>
-    <t>133585508</t>
+    <t>Relatório Recusas Santander- 31.07.2025</t>
+  </si>
+  <si>
+    <t>133504944</t>
+  </si>
+  <si>
+    <t>133520636</t>
+  </si>
+  <si>
+    <t>133587093</t>
+  </si>
+  <si>
+    <t>133604806</t>
+  </si>
+  <si>
+    <t>133623704</t>
+  </si>
+  <si>
+    <t>133660041</t>
+  </si>
+  <si>
+    <t>133657083</t>
+  </si>
+  <si>
+    <t>133678116</t>
+  </si>
+  <si>
+    <t>133568893</t>
+  </si>
+  <si>
+    <t>133591971</t>
+  </si>
+  <si>
+    <t>133699787</t>
+  </si>
+  <si>
+    <t>133596080</t>
+  </si>
+  <si>
+    <t>133575328</t>
+  </si>
+  <si>
+    <t>133579818</t>
+  </si>
+  <si>
+    <t>133583157</t>
+  </si>
+  <si>
+    <t>133587403</t>
+  </si>
+  <si>
+    <t>133587604</t>
+  </si>
+  <si>
+    <t>133587995</t>
   </si>
 </sst>
 </file>
@@ -542,7 +521,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -912,135 +891,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D31" s="6"/>
+      <c r="D21" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
